--- a/data/environmental_facilities/data.xlsx
+++ b/data/environmental_facilities/data.xlsx
@@ -533,7 +533,7 @@
         <v>087-839-3990</v>
       </c>
       <c r="G4" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/shinotorikumi/soshikihyo/eisei.html</v>
+        <v>https://www.city.takamatsu.kagawa.jp/kurashi/kurashi/gomi/sinyou/index.html</v>
       </c>
       <c r="H4" t="str">
         <v/>
